--- a/source/Transmittal.Reports.OpenXML/Reports/TransmittalSummary.xlsx
+++ b/source/Transmittal.Reports.OpenXML/Reports/TransmittalSummary.xlsx
@@ -8,13 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8cb514c15eb25f74/Transmittal Testing/Reports/Style3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{9965DD62-E1C7-420B-9F8D-E1A0EC2C1FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E121A6F-37DD-448B-B0B0-B9A4DE044A66}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{9965DD62-E1C7-420B-9F8D-E1A0EC2C1FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5F57480-A63E-46C6-9CB9-386B10042344}"/>
   <bookViews>
-    <workbookView xWindow="9870" yWindow="4095" windowWidth="31395" windowHeight="18090" xr2:uid="{606C6374-EA5B-4411-AC94-0D7407AA4B49}"/>
+    <workbookView xWindow="19260" yWindow="1860" windowWidth="35145" windowHeight="19230" xr2:uid="{606C6374-EA5B-4411-AC94-0D7407AA4B49}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="DistributionListData">Summary!$A$15:$D$15</definedName>
+    <definedName name="SheetListData">Summary!$A$12:$D$12</definedName>
+    <definedName name="SummaryColumnData">Summary!$D$7:$D$15</definedName>
+    <definedName name="TransmittalFormatData">Summary!$D$14</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>{{ReportTitle}}</t>
   </si>
@@ -65,13 +71,46 @@
     <t>Paper</t>
   </si>
   <si>
-    <t>Rev</t>
-  </si>
-  <si>
     <t>Company</t>
   </si>
   <si>
     <t>Person</t>
+  </si>
+  <si>
+    <t>Document ID format: &lt;Project&gt;-&lt;Originator&gt;-&lt;Volume&gt;-&lt;Level&gt;-&lt;Type&gt;-&lt;Role&gt;-&lt;DocNo&gt;</t>
+  </si>
+  <si>
+    <t>{{DrgName}}</t>
+  </si>
+  <si>
+    <t>{{DrgRev}}</t>
+  </si>
+  <si>
+    <t>{{DrgPaper}}</t>
+  </si>
+  <si>
+    <t>{{DateYear}}</t>
+  </si>
+  <si>
+    <t>{{DateMonth}}</t>
+  </si>
+  <si>
+    <t>{{DateDay}}</t>
+  </si>
+  <si>
+    <t>{{TransCopies}}</t>
+  </si>
+  <si>
+    <t>{{PersonName}}</t>
+  </si>
+  <si>
+    <t>{{CompanyName}}</t>
+  </si>
+  <si>
+    <t>{{TransFormat}}</t>
+  </si>
+  <si>
+    <t>{{DrgProj}}-{{DrgOriginator}}-{{DrgVolume}}-{{DrgLevel}}-{{DrgType}}-{{DrgRole}}-{{DrgNumber}}</t>
   </si>
 </sst>
 </file>
@@ -123,10 +162,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,68 +507,117 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A1324D-5174-494B-85F7-F95A31C872BA}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.85546875" customWidth="1"/>
     <col min="2" max="2" width="35.42578125" customWidth="1"/>
     <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>11</v>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/source/Transmittal.Reports.OpenXML/Reports/TransmittalSummary.xlsx
+++ b/source/Transmittal.Reports.OpenXML/Reports/TransmittalSummary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8cb514c15eb25f74/Transmittal Testing/Reports/Style3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Source\Repos\Transmittal\source\Transmittal.Reports.OpenXML\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{9965DD62-E1C7-420B-9F8D-E1A0EC2C1FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5F57480-A63E-46C6-9CB9-386B10042344}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672B0CD7-3443-4A4F-9583-929747B6345A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19260" yWindow="1860" windowWidth="35145" windowHeight="19230" xr2:uid="{606C6374-EA5B-4411-AC94-0D7407AA4B49}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="34185" windowHeight="19650" xr2:uid="{606C6374-EA5B-4411-AC94-0D7407AA4B49}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -184,10 +184,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
